--- a/life_table2_worked.xlsx
+++ b/life_table2_worked.xlsx
@@ -1,25 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\NRES-470\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1419D630-3E11-44E7-B1A9-5041572549E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="life_table2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>x (age)</t>
   </si>
@@ -47,11 +62,14 @@
   <si>
     <t>r</t>
   </si>
+  <si>
+    <t>g(x)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -851,11 +869,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -874,8 +892,11 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -897,8 +918,12 @@
         <f>E2*A2</f>
         <v>0</v>
       </c>
+      <c r="G2">
+        <f>B3/B2</f>
+        <v>0.4375</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -920,8 +945,12 @@
         <f t="shared" ref="F3:F7" si="2">E3*A3</f>
         <v>0.35000000000000003</v>
       </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G6" si="3">B4/B3</f>
+        <v>0.58857142857142852</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -943,8 +972,12 @@
         <f t="shared" si="2"/>
         <v>1.236</v>
       </c>
+      <c r="G4">
+        <f t="shared" si="3"/>
+        <v>0.43689320388349512</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -966,8 +999,12 @@
         <f t="shared" si="2"/>
         <v>0.97875000000000001</v>
       </c>
+      <c r="G5">
+        <f t="shared" si="3"/>
+        <v>0.42222222222222222</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -989,8 +1026,12 @@
         <f t="shared" si="2"/>
         <v>7.6000000000000012E-2</v>
       </c>
+      <c r="G6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1013,7 +1054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1022,7 +1063,7 @@
         <v>1.3132499999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1031,7 +1072,7 @@
         <v>2.0108509423186756</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
